--- a/public/templates/Product_Import_Template.xlsx
+++ b/public/templates/Product_Import_Template.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -422,13 +422,13 @@
         <v>Selling Price (Optional)</v>
       </c>
       <c r="H1" t="str">
-        <v>Dealer Price (Optional)</v>
+        <v>Supplier (Optional)</v>
       </c>
       <c r="I1" t="str">
-        <v>Supplier (Optional)</v>
+        <v>Business Unit (Optional)</v>
       </c>
       <c r="J1" t="str">
-        <v>Business Unit (Optional)</v>
+        <v>Must Sale (Optional)</v>
       </c>
       <c r="K1" t="str">
         <v>Description (Optional)</v>
@@ -466,13 +466,13 @@
         <v>6500</v>
       </c>
       <c r="H2" t="str">
-        <v>5800</v>
+        <v>Alpha Pharma</v>
       </c>
       <c r="I2" t="str">
-        <v>Alpha Pharma</v>
+        <v>Medical</v>
       </c>
       <c r="J2" t="str">
-        <v>Medical</v>
+        <v>Yes</v>
       </c>
       <c r="K2" t="str">
         <v>Standard antibiotic</v>
@@ -485,11 +485,55 @@
       </c>
       <c r="N2" t="str">
         <v>Capsule</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>PRD-002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>SKU-1002</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Paracetamol 500mg</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Analgesics</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F3" t="str">
+        <v>1200</v>
+      </c>
+      <c r="G3" t="str">
+        <v>1800</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Mega Life</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Consumer Health</v>
+      </c>
+      <c r="J3" t="str">
+        <v>No</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Pain and fever relief</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Paracetamol</v>
+      </c>
+      <c r="M3" t="str">
+        <v>Panadol</v>
+      </c>
+      <c r="N3" t="str">
+        <v>Tablet</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/templates/Product_Import_Template.xlsx
+++ b/public/templates/Product_Import_Template.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N101"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -459,10 +459,10 @@
       <c r="E2" t="str">
         <v>Box</v>
       </c>
-      <c r="F2" t="str">
-        <v>5000</v>
-      </c>
-      <c r="G2" t="str">
+      <c r="F2">
+        <v>4500</v>
+      </c>
+      <c r="G2">
         <v>6500</v>
       </c>
       <c r="H2" t="str">
@@ -475,7 +475,7 @@
         <v>Yes</v>
       </c>
       <c r="K2" t="str">
-        <v>Standard antibiotic</v>
+        <v>Amoxicillin 500mg (Amoxicillin) pharmaceutical grade</v>
       </c>
       <c r="L2" t="str">
         <v>Amoxicillin</v>
@@ -495,45 +495,4357 @@
         <v>SKU-1002</v>
       </c>
       <c r="C3" t="str">
+        <v>Amoxicillin &amp; Clavulanate 625mg</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Antibiotics</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F3">
+        <v>12000</v>
+      </c>
+      <c r="G3">
+        <v>16500</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Alpha Pharma</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Medical</v>
+      </c>
+      <c r="J3" t="str">
+        <v>No</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Amoxicillin &amp; Clavulanate 625mg (Amoxicillin + Clavulanic Acid) pharmaceutical grade</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Amoxicillin + Clavulanic Acid</v>
+      </c>
+      <c r="M3" t="str">
+        <v>Augmentin</v>
+      </c>
+      <c r="N3" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>PRD-003</v>
+      </c>
+      <c r="B4" t="str">
+        <v>SKU-1003</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Azithromycin 500mg</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Antibiotics</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F4">
+        <v>8500</v>
+      </c>
+      <c r="G4">
+        <v>11500</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Apex Healthcare</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Medical</v>
+      </c>
+      <c r="J4" t="str">
+        <v>No</v>
+      </c>
+      <c r="K4" t="str">
+        <v>Azithromycin 500mg (Azithromycin) pharmaceutical grade</v>
+      </c>
+      <c r="L4" t="str">
+        <v>Azithromycin</v>
+      </c>
+      <c r="M4" t="str">
+        <v>Zithromax</v>
+      </c>
+      <c r="N4" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>PRD-004</v>
+      </c>
+      <c r="B5" t="str">
+        <v>SKU-1004</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Cefixime 200mg</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Antibiotics</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F5">
+        <v>11000</v>
+      </c>
+      <c r="G5">
+        <v>15000</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Apex Healthcare</v>
+      </c>
+      <c r="I5" t="str">
+        <v>Medical</v>
+      </c>
+      <c r="J5" t="str">
+        <v>No</v>
+      </c>
+      <c r="K5" t="str">
+        <v>Cefixime 200mg (Cefixime) pharmaceutical grade</v>
+      </c>
+      <c r="L5" t="str">
+        <v>Cefixime</v>
+      </c>
+      <c r="M5" t="str">
+        <v>Cefspan</v>
+      </c>
+      <c r="N5" t="str">
+        <v>Capsule</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>PRD-005</v>
+      </c>
+      <c r="B6" t="str">
+        <v>SKU-1005</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Ciprofloxacin 500mg</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Antibiotics</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F6">
+        <v>5000</v>
+      </c>
+      <c r="G6">
+        <v>7200</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Grand Pharma</v>
+      </c>
+      <c r="I6" t="str">
+        <v>Medical</v>
+      </c>
+      <c r="J6" t="str">
+        <v>No</v>
+      </c>
+      <c r="K6" t="str">
+        <v>Ciprofloxacin 500mg (Ciprofloxacin) pharmaceutical grade</v>
+      </c>
+      <c r="L6" t="str">
+        <v>Ciprofloxacin</v>
+      </c>
+      <c r="M6" t="str">
+        <v>Ciprobay</v>
+      </c>
+      <c r="N6" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>PRD-006</v>
+      </c>
+      <c r="B7" t="str">
+        <v>SKU-1006</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Levofloxacin 500mg</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Antibiotics</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F7">
+        <v>9500</v>
+      </c>
+      <c r="G7">
+        <v>13500</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Grand Pharma</v>
+      </c>
+      <c r="I7" t="str">
+        <v>Medical</v>
+      </c>
+      <c r="J7" t="str">
+        <v>No</v>
+      </c>
+      <c r="K7" t="str">
+        <v>Levofloxacin 500mg (Levofloxacin) pharmaceutical grade</v>
+      </c>
+      <c r="L7" t="str">
+        <v>Levofloxacin</v>
+      </c>
+      <c r="M7" t="str">
+        <v>Cravit</v>
+      </c>
+      <c r="N7" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>PRD-007</v>
+      </c>
+      <c r="B8" t="str">
+        <v>SKU-1007</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Cephalexin 500mg</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Antibiotics</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F8">
+        <v>6000</v>
+      </c>
+      <c r="G8">
+        <v>8500</v>
+      </c>
+      <c r="H8" t="str">
+        <v>Alpha Pharma</v>
+      </c>
+      <c r="I8" t="str">
+        <v>Medical</v>
+      </c>
+      <c r="J8" t="str">
+        <v>No</v>
+      </c>
+      <c r="K8" t="str">
+        <v>Cephalexin 500mg (Cephalexin) pharmaceutical grade</v>
+      </c>
+      <c r="L8" t="str">
+        <v>Cephalexin</v>
+      </c>
+      <c r="M8" t="str">
+        <v>Keflex</v>
+      </c>
+      <c r="N8" t="str">
+        <v>Capsule</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>PRD-008</v>
+      </c>
+      <c r="B9" t="str">
+        <v>SKU-1008</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Clarithromycin 500mg</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Antibiotics</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F9">
+        <v>14000</v>
+      </c>
+      <c r="G9">
+        <v>19000</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Apex Healthcare</v>
+      </c>
+      <c r="I9" t="str">
+        <v>Medical</v>
+      </c>
+      <c r="J9" t="str">
+        <v>No</v>
+      </c>
+      <c r="K9" t="str">
+        <v>Clarithromycin 500mg (Clarithromycin) pharmaceutical grade</v>
+      </c>
+      <c r="L9" t="str">
+        <v>Clarithromycin</v>
+      </c>
+      <c r="M9" t="str">
+        <v>Klacid</v>
+      </c>
+      <c r="N9" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>PRD-009</v>
+      </c>
+      <c r="B10" t="str">
+        <v>SKU-1009</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Doxycycline 100mg</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Antibiotics</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F10">
+        <v>3500</v>
+      </c>
+      <c r="G10">
+        <v>5000</v>
+      </c>
+      <c r="H10" t="str">
+        <v>BioMed Myanmar</v>
+      </c>
+      <c r="I10" t="str">
+        <v>Medical</v>
+      </c>
+      <c r="J10" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="K10" t="str">
+        <v>Doxycycline 100mg (Doxycycline) pharmaceutical grade</v>
+      </c>
+      <c r="L10" t="str">
+        <v>Doxycycline</v>
+      </c>
+      <c r="M10" t="str">
+        <v>Vibramycin</v>
+      </c>
+      <c r="N10" t="str">
+        <v>Capsule</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>PRD-010</v>
+      </c>
+      <c r="B11" t="str">
+        <v>SKU-1010</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Metronidazole 400mg</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Antibiotics</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F11">
+        <v>2500</v>
+      </c>
+      <c r="G11">
+        <v>3800</v>
+      </c>
+      <c r="H11" t="str">
+        <v>BioMed Myanmar</v>
+      </c>
+      <c r="I11" t="str">
+        <v>Medical</v>
+      </c>
+      <c r="J11" t="str">
+        <v>No</v>
+      </c>
+      <c r="K11" t="str">
+        <v>Metronidazole 400mg (Metronidazole) pharmaceutical grade</v>
+      </c>
+      <c r="L11" t="str">
+        <v>Metronidazole</v>
+      </c>
+      <c r="M11" t="str">
+        <v>Flagyl</v>
+      </c>
+      <c r="N11" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>PRD-011</v>
+      </c>
+      <c r="B12" t="str">
+        <v>SKU-1011</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Ceftriaxone 1g Injection</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Antibiotics</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Vial</v>
+      </c>
+      <c r="F12">
+        <v>4000</v>
+      </c>
+      <c r="G12">
+        <v>6000</v>
+      </c>
+      <c r="H12" t="str">
+        <v>Grand Pharma</v>
+      </c>
+      <c r="I12" t="str">
+        <v>Hospital Care</v>
+      </c>
+      <c r="J12" t="str">
+        <v>No</v>
+      </c>
+      <c r="K12" t="str">
+        <v>Ceftriaxone 1g Injection (Ceftriaxone) pharmaceutical grade</v>
+      </c>
+      <c r="L12" t="str">
+        <v>Ceftriaxone</v>
+      </c>
+      <c r="M12" t="str">
+        <v>Rocephin</v>
+      </c>
+      <c r="N12" t="str">
+        <v>Vial</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>PRD-012</v>
+      </c>
+      <c r="B13" t="str">
+        <v>SKU-1012</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Meropenem 1g Injection</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Antibiotics</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Vial</v>
+      </c>
+      <c r="F13">
+        <v>22000</v>
+      </c>
+      <c r="G13">
+        <v>30000</v>
+      </c>
+      <c r="H13" t="str">
+        <v>Grand Pharma</v>
+      </c>
+      <c r="I13" t="str">
+        <v>Hospital Care</v>
+      </c>
+      <c r="J13" t="str">
+        <v>No</v>
+      </c>
+      <c r="K13" t="str">
+        <v>Meropenem 1g Injection (Meropenem) pharmaceutical grade</v>
+      </c>
+      <c r="L13" t="str">
+        <v>Meropenem</v>
+      </c>
+      <c r="M13" t="str">
+        <v>Meronem</v>
+      </c>
+      <c r="N13" t="str">
+        <v>Vial</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>PRD-013</v>
+      </c>
+      <c r="B14" t="str">
+        <v>SKU-1013</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Ampicillin 500mg</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Antibiotics</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F14">
+        <v>4000</v>
+      </c>
+      <c r="G14">
+        <v>5800</v>
+      </c>
+      <c r="H14" t="str">
+        <v>Alpha Pharma</v>
+      </c>
+      <c r="I14" t="str">
+        <v>Medical</v>
+      </c>
+      <c r="J14" t="str">
+        <v>No</v>
+      </c>
+      <c r="K14" t="str">
+        <v>Ampicillin 500mg (Ampicillin) pharmaceutical grade</v>
+      </c>
+      <c r="L14" t="str">
+        <v>Ampicillin</v>
+      </c>
+      <c r="M14" t="str">
+        <v>Omnipen</v>
+      </c>
+      <c r="N14" t="str">
+        <v>Capsule</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>PRD-014</v>
+      </c>
+      <c r="B15" t="str">
+        <v>SKU-1014</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Cefuroxime Axetil 500mg</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Antibiotics</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F15">
+        <v>16000</v>
+      </c>
+      <c r="G15">
+        <v>22000</v>
+      </c>
+      <c r="H15" t="str">
+        <v>Apex Healthcare</v>
+      </c>
+      <c r="I15" t="str">
+        <v>Medical</v>
+      </c>
+      <c r="J15" t="str">
+        <v>No</v>
+      </c>
+      <c r="K15" t="str">
+        <v>Cefuroxime Axetil 500mg (Cefuroxime) pharmaceutical grade</v>
+      </c>
+      <c r="L15" t="str">
+        <v>Cefuroxime</v>
+      </c>
+      <c r="M15" t="str">
+        <v>Zinnat</v>
+      </c>
+      <c r="N15" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>PRD-015</v>
+      </c>
+      <c r="B16" t="str">
+        <v>SKU-1015</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Erythromycin 250mg</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Antibiotics</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F16">
+        <v>4800</v>
+      </c>
+      <c r="G16">
+        <v>7000</v>
+      </c>
+      <c r="H16" t="str">
+        <v>BioMed Myanmar</v>
+      </c>
+      <c r="I16" t="str">
+        <v>Medical</v>
+      </c>
+      <c r="J16" t="str">
+        <v>No</v>
+      </c>
+      <c r="K16" t="str">
+        <v>Erythromycin 250mg (Erythromycin) pharmaceutical grade</v>
+      </c>
+      <c r="L16" t="str">
+        <v>Erythromycin</v>
+      </c>
+      <c r="M16" t="str">
+        <v>Erythrocin</v>
+      </c>
+      <c r="N16" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>PRD-016</v>
+      </c>
+      <c r="B17" t="str">
+        <v>SKU-1016</v>
+      </c>
+      <c r="C17" t="str">
         <v>Paracetamol 500mg</v>
       </c>
-      <c r="D3" t="str">
+      <c r="D17" t="str">
         <v>Analgesics</v>
       </c>
-      <c r="E3" t="str">
-        <v>Box</v>
-      </c>
-      <c r="F3" t="str">
+      <c r="E17" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F17">
         <v>1200</v>
       </c>
-      <c r="G3" t="str">
+      <c r="G17">
         <v>1800</v>
       </c>
-      <c r="H3" t="str">
-        <v>Mega Life</v>
-      </c>
-      <c r="I3" t="str">
+      <c r="H17" t="str">
+        <v>Mega Life Sciences</v>
+      </c>
+      <c r="I17" t="str">
         <v>Consumer Health</v>
       </c>
-      <c r="J3" t="str">
-        <v>No</v>
-      </c>
-      <c r="K3" t="str">
-        <v>Pain and fever relief</v>
-      </c>
-      <c r="L3" t="str">
+      <c r="J17" t="str">
+        <v>No</v>
+      </c>
+      <c r="K17" t="str">
+        <v>Paracetamol 500mg (Paracetamol) pharmaceutical grade</v>
+      </c>
+      <c r="L17" t="str">
         <v>Paracetamol</v>
       </c>
-      <c r="M3" t="str">
-        <v>Panadol</v>
-      </c>
-      <c r="N3" t="str">
-        <v>Tablet</v>
+      <c r="M17" t="str">
+        <v>Biogesic</v>
+      </c>
+      <c r="N17" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>PRD-017</v>
+      </c>
+      <c r="B18" t="str">
+        <v>SKU-1017</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Paracetamol Extra (with Caffeine)</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Analgesics</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F18">
+        <v>2200</v>
+      </c>
+      <c r="G18">
+        <v>3200</v>
+      </c>
+      <c r="H18" t="str">
+        <v>Mega Life Sciences</v>
+      </c>
+      <c r="I18" t="str">
+        <v>Consumer Health</v>
+      </c>
+      <c r="J18" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="K18" t="str">
+        <v>Paracetamol Extra (with Caffeine) (Paracetamol + Caffeine) pharmaceutical grade</v>
+      </c>
+      <c r="L18" t="str">
+        <v>Paracetamol + Caffeine</v>
+      </c>
+      <c r="M18" t="str">
+        <v>Panadol Extra</v>
+      </c>
+      <c r="N18" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>PRD-018</v>
+      </c>
+      <c r="B19" t="str">
+        <v>SKU-1018</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Ibuprofen 400mg</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Analgesics</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F19">
+        <v>2800</v>
+      </c>
+      <c r="G19">
+        <v>4200</v>
+      </c>
+      <c r="H19" t="str">
+        <v>Mega Life Sciences</v>
+      </c>
+      <c r="I19" t="str">
+        <v>Consumer Health</v>
+      </c>
+      <c r="J19" t="str">
+        <v>No</v>
+      </c>
+      <c r="K19" t="str">
+        <v>Ibuprofen 400mg (Ibuprofen) pharmaceutical grade</v>
+      </c>
+      <c r="L19" t="str">
+        <v>Ibuprofen</v>
+      </c>
+      <c r="M19" t="str">
+        <v>Brufen</v>
+      </c>
+      <c r="N19" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>PRD-019</v>
+      </c>
+      <c r="B20" t="str">
+        <v>SKU-1019</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Mefenamic Acid 500mg</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Analgesics</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F20">
+        <v>3500</v>
+      </c>
+      <c r="G20">
+        <v>5200</v>
+      </c>
+      <c r="H20" t="str">
+        <v>Apex Healthcare</v>
+      </c>
+      <c r="I20" t="str">
+        <v>Medical</v>
+      </c>
+      <c r="J20" t="str">
+        <v>No</v>
+      </c>
+      <c r="K20" t="str">
+        <v>Mefenamic Acid 500mg (Mefenamic Acid) pharmaceutical grade</v>
+      </c>
+      <c r="L20" t="str">
+        <v>Mefenamic Acid</v>
+      </c>
+      <c r="M20" t="str">
+        <v>Ponstan</v>
+      </c>
+      <c r="N20" t="str">
+        <v>Capsule</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>PRD-020</v>
+      </c>
+      <c r="B21" t="str">
+        <v>SKU-1020</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Diclofenac Sodium 50mg</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Analgesics</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F21">
+        <v>2600</v>
+      </c>
+      <c r="G21">
+        <v>4000</v>
+      </c>
+      <c r="H21" t="str">
+        <v>Novartis Alliance</v>
+      </c>
+      <c r="I21" t="str">
+        <v>Medical</v>
+      </c>
+      <c r="J21" t="str">
+        <v>No</v>
+      </c>
+      <c r="K21" t="str">
+        <v>Diclofenac Sodium 50mg (Diclofenac) pharmaceutical grade</v>
+      </c>
+      <c r="L21" t="str">
+        <v>Diclofenac</v>
+      </c>
+      <c r="M21" t="str">
+        <v>Voltaren</v>
+      </c>
+      <c r="N21" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>PRD-021</v>
+      </c>
+      <c r="B22" t="str">
+        <v>SKU-1021</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Diclofenac Emulgel 20g</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Analgesics</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Tube</v>
+      </c>
+      <c r="F22">
+        <v>4200</v>
+      </c>
+      <c r="G22">
+        <v>6200</v>
+      </c>
+      <c r="H22" t="str">
+        <v>Novartis Alliance</v>
+      </c>
+      <c r="I22" t="str">
+        <v>Consumer Health</v>
+      </c>
+      <c r="J22" t="str">
+        <v>No</v>
+      </c>
+      <c r="K22" t="str">
+        <v>Diclofenac Emulgel 20g (Diclofenac Diethylamine) pharmaceutical grade</v>
+      </c>
+      <c r="L22" t="str">
+        <v>Diclofenac Diethylamine</v>
+      </c>
+      <c r="M22" t="str">
+        <v>Voltaren Emulgel</v>
+      </c>
+      <c r="N22" t="str">
+        <v>Tube</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>PRD-022</v>
+      </c>
+      <c r="B23" t="str">
+        <v>SKU-1022</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Tramadol 50mg</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Analgesics</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F23">
+        <v>5500</v>
+      </c>
+      <c r="G23">
+        <v>8000</v>
+      </c>
+      <c r="H23" t="str">
+        <v>Grand Pharma</v>
+      </c>
+      <c r="I23" t="str">
+        <v>Medical</v>
+      </c>
+      <c r="J23" t="str">
+        <v>No</v>
+      </c>
+      <c r="K23" t="str">
+        <v>Tramadol 50mg (Tramadol) pharmaceutical grade</v>
+      </c>
+      <c r="L23" t="str">
+        <v>Tramadol</v>
+      </c>
+      <c r="M23" t="str">
+        <v>Ultram</v>
+      </c>
+      <c r="N23" t="str">
+        <v>Capsule</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>PRD-023</v>
+      </c>
+      <c r="B24" t="str">
+        <v>SKU-1023</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Aceclofenac 100mg</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Analgesics</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F24">
+        <v>3800</v>
+      </c>
+      <c r="G24">
+        <v>5600</v>
+      </c>
+      <c r="H24" t="str">
+        <v>Sun Pharma Group</v>
+      </c>
+      <c r="I24" t="str">
+        <v>Medical</v>
+      </c>
+      <c r="J24" t="str">
+        <v>No</v>
+      </c>
+      <c r="K24" t="str">
+        <v>Aceclofenac 100mg (Aceclofenac) pharmaceutical grade</v>
+      </c>
+      <c r="L24" t="str">
+        <v>Aceclofenac</v>
+      </c>
+      <c r="M24" t="str">
+        <v>Hifenac</v>
+      </c>
+      <c r="N24" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>PRD-024</v>
+      </c>
+      <c r="B25" t="str">
+        <v>SKU-1024</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Celecoxib 200mg</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Analgesics</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F25">
+        <v>11000</v>
+      </c>
+      <c r="G25">
+        <v>15500</v>
+      </c>
+      <c r="H25" t="str">
+        <v>Novartis Alliance</v>
+      </c>
+      <c r="I25" t="str">
+        <v>Specialty Pharma</v>
+      </c>
+      <c r="J25" t="str">
+        <v>No</v>
+      </c>
+      <c r="K25" t="str">
+        <v>Celecoxib 200mg (Celecoxib) pharmaceutical grade</v>
+      </c>
+      <c r="L25" t="str">
+        <v>Celecoxib</v>
+      </c>
+      <c r="M25" t="str">
+        <v>Celebrex</v>
+      </c>
+      <c r="N25" t="str">
+        <v>Capsule</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>PRD-025</v>
+      </c>
+      <c r="B26" t="str">
+        <v>SKU-1025</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Etoricoxib 90mg</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Analgesics</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F26">
+        <v>13500</v>
+      </c>
+      <c r="G26">
+        <v>18500</v>
+      </c>
+      <c r="H26" t="str">
+        <v>Novartis Alliance</v>
+      </c>
+      <c r="I26" t="str">
+        <v>Specialty Pharma</v>
+      </c>
+      <c r="J26" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="K26" t="str">
+        <v>Etoricoxib 90mg (Etoricoxib) pharmaceutical grade</v>
+      </c>
+      <c r="L26" t="str">
+        <v>Etoricoxib</v>
+      </c>
+      <c r="M26" t="str">
+        <v>Arcoxia</v>
+      </c>
+      <c r="N26" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>PRD-026</v>
+      </c>
+      <c r="B27" t="str">
+        <v>SKU-1026</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Paracetamol Syrup 120mg/5ml</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Analgesics</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Bottle</v>
+      </c>
+      <c r="F27">
+        <v>1800</v>
+      </c>
+      <c r="G27">
+        <v>2700</v>
+      </c>
+      <c r="H27" t="str">
+        <v>Mega Life Sciences</v>
+      </c>
+      <c r="I27" t="str">
+        <v>Consumer Health</v>
+      </c>
+      <c r="J27" t="str">
+        <v>No</v>
+      </c>
+      <c r="K27" t="str">
+        <v>Paracetamol Syrup 120mg/5ml (Paracetamol) pharmaceutical grade</v>
+      </c>
+      <c r="L27" t="str">
+        <v>Paracetamol</v>
+      </c>
+      <c r="M27" t="str">
+        <v>Calpol</v>
+      </c>
+      <c r="N27" t="str">
+        <v>Bottle</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>PRD-027</v>
+      </c>
+      <c r="B28" t="str">
+        <v>SKU-1027</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Ketorolac 30mg Injection</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Analgesics</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Ampoule</v>
+      </c>
+      <c r="F28">
+        <v>3000</v>
+      </c>
+      <c r="G28">
+        <v>4500</v>
+      </c>
+      <c r="H28" t="str">
+        <v>Grand Pharma</v>
+      </c>
+      <c r="I28" t="str">
+        <v>Hospital Care</v>
+      </c>
+      <c r="J28" t="str">
+        <v>No</v>
+      </c>
+      <c r="K28" t="str">
+        <v>Ketorolac 30mg Injection (Ketorolac) pharmaceutical grade</v>
+      </c>
+      <c r="L28" t="str">
+        <v>Ketorolac</v>
+      </c>
+      <c r="M28" t="str">
+        <v>Toradol</v>
+      </c>
+      <c r="N28" t="str">
+        <v>Ampoule</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>PRD-028</v>
+      </c>
+      <c r="B29" t="str">
+        <v>SKU-1028</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Omeprazole 20mg</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Gastrointestinal</v>
+      </c>
+      <c r="E29" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F29">
+        <v>3200</v>
+      </c>
+      <c r="G29">
+        <v>4800</v>
+      </c>
+      <c r="H29" t="str">
+        <v>Alpha Pharma</v>
+      </c>
+      <c r="I29" t="str">
+        <v>Medical</v>
+      </c>
+      <c r="J29" t="str">
+        <v>No</v>
+      </c>
+      <c r="K29" t="str">
+        <v>Omeprazole 20mg (Omeprazole) pharmaceutical grade</v>
+      </c>
+      <c r="L29" t="str">
+        <v>Omeprazole</v>
+      </c>
+      <c r="M29" t="str">
+        <v>Losec</v>
+      </c>
+      <c r="N29" t="str">
+        <v>Capsule</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>PRD-029</v>
+      </c>
+      <c r="B30" t="str">
+        <v>SKU-1029</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Esomeprazole 40mg</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Gastrointestinal</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F30">
+        <v>9500</v>
+      </c>
+      <c r="G30">
+        <v>13500</v>
+      </c>
+      <c r="H30" t="str">
+        <v>Apex Healthcare</v>
+      </c>
+      <c r="I30" t="str">
+        <v>Specialty Pharma</v>
+      </c>
+      <c r="J30" t="str">
+        <v>No</v>
+      </c>
+      <c r="K30" t="str">
+        <v>Esomeprazole 40mg (Esomeprazole) pharmaceutical grade</v>
+      </c>
+      <c r="L30" t="str">
+        <v>Esomeprazole</v>
+      </c>
+      <c r="M30" t="str">
+        <v>Nexium</v>
+      </c>
+      <c r="N30" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>PRD-030</v>
+      </c>
+      <c r="B31" t="str">
+        <v>SKU-1030</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Pantoprazole 40mg</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Gastrointestinal</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F31">
+        <v>6200</v>
+      </c>
+      <c r="G31">
+        <v>8800</v>
+      </c>
+      <c r="H31" t="str">
+        <v>Sun Pharma Group</v>
+      </c>
+      <c r="I31" t="str">
+        <v>Medical</v>
+      </c>
+      <c r="J31" t="str">
+        <v>No</v>
+      </c>
+      <c r="K31" t="str">
+        <v>Pantoprazole 40mg (Pantoprazole) pharmaceutical grade</v>
+      </c>
+      <c r="L31" t="str">
+        <v>Pantoprazole</v>
+      </c>
+      <c r="M31" t="str">
+        <v>Pantocid</v>
+      </c>
+      <c r="N31" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>PRD-031</v>
+      </c>
+      <c r="B32" t="str">
+        <v>SKU-1031</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Rabeprazole 20mg</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Gastrointestinal</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F32">
+        <v>8000</v>
+      </c>
+      <c r="G32">
+        <v>11500</v>
+      </c>
+      <c r="H32" t="str">
+        <v>Sun Pharma Group</v>
+      </c>
+      <c r="I32" t="str">
+        <v>Medical</v>
+      </c>
+      <c r="J32" t="str">
+        <v>No</v>
+      </c>
+      <c r="K32" t="str">
+        <v>Rabeprazole 20mg (Rabeprazole) pharmaceutical grade</v>
+      </c>
+      <c r="L32" t="str">
+        <v>Rabeprazole</v>
+      </c>
+      <c r="M32" t="str">
+        <v>Pariet</v>
+      </c>
+      <c r="N32" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>PRD-032</v>
+      </c>
+      <c r="B33" t="str">
+        <v>SKU-1032</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Domperidone 10mg</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Gastrointestinal</v>
+      </c>
+      <c r="E33" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F33">
+        <v>2500</v>
+      </c>
+      <c r="G33">
+        <v>3800</v>
+      </c>
+      <c r="H33" t="str">
+        <v>Mega Life Sciences</v>
+      </c>
+      <c r="I33" t="str">
+        <v>Consumer Health</v>
+      </c>
+      <c r="J33" t="str">
+        <v>No</v>
+      </c>
+      <c r="K33" t="str">
+        <v>Domperidone 10mg (Domperidone) pharmaceutical grade</v>
+      </c>
+      <c r="L33" t="str">
+        <v>Domperidone</v>
+      </c>
+      <c r="M33" t="str">
+        <v>Motilium</v>
+      </c>
+      <c r="N33" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>PRD-033</v>
+      </c>
+      <c r="B34" t="str">
+        <v>SKU-1033</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Ondansetron 8mg</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Gastrointestinal</v>
+      </c>
+      <c r="E34" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F34">
+        <v>5500</v>
+      </c>
+      <c r="G34">
+        <v>8000</v>
+      </c>
+      <c r="H34" t="str">
+        <v>Grand Pharma</v>
+      </c>
+      <c r="I34" t="str">
+        <v>Medical</v>
+      </c>
+      <c r="J34" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="K34" t="str">
+        <v>Ondansetron 8mg (Ondansetron) pharmaceutical grade</v>
+      </c>
+      <c r="L34" t="str">
+        <v>Ondansetron</v>
+      </c>
+      <c r="M34" t="str">
+        <v>Zofran</v>
+      </c>
+      <c r="N34" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>PRD-034</v>
+      </c>
+      <c r="B35" t="str">
+        <v>SKU-1034</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Loperamide 2mg</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Gastrointestinal</v>
+      </c>
+      <c r="E35" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F35">
+        <v>2000</v>
+      </c>
+      <c r="G35">
+        <v>3000</v>
+      </c>
+      <c r="H35" t="str">
+        <v>Mega Life Sciences</v>
+      </c>
+      <c r="I35" t="str">
+        <v>Consumer Health</v>
+      </c>
+      <c r="J35" t="str">
+        <v>No</v>
+      </c>
+      <c r="K35" t="str">
+        <v>Loperamide 2mg (Loperamide) pharmaceutical grade</v>
+      </c>
+      <c r="L35" t="str">
+        <v>Loperamide</v>
+      </c>
+      <c r="M35" t="str">
+        <v>Imodium</v>
+      </c>
+      <c r="N35" t="str">
+        <v>Capsule</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>PRD-035</v>
+      </c>
+      <c r="B36" t="str">
+        <v>SKU-1035</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Oral Rehydration Salts (ORS)</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Gastrointestinal</v>
+      </c>
+      <c r="E36" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F36">
+        <v>1500</v>
+      </c>
+      <c r="G36">
+        <v>2300</v>
+      </c>
+      <c r="H36" t="str">
+        <v>Mega Life Sciences</v>
+      </c>
+      <c r="I36" t="str">
+        <v>Consumer Health</v>
+      </c>
+      <c r="J36" t="str">
+        <v>No</v>
+      </c>
+      <c r="K36" t="str">
+        <v>Oral Rehydration Salts (ORS) (Oral Electrolytes) pharmaceutical grade</v>
+      </c>
+      <c r="L36" t="str">
+        <v>Oral Electrolytes</v>
+      </c>
+      <c r="M36" t="str">
+        <v>Hydralyte</v>
+      </c>
+      <c r="N36" t="str">
+        <v>Box</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>PRD-036</v>
+      </c>
+      <c r="B37" t="str">
+        <v>SKU-1036</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Antacid Gel Suspension 240ml</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Gastrointestinal</v>
+      </c>
+      <c r="E37" t="str">
+        <v>Bottle</v>
+      </c>
+      <c r="F37">
+        <v>3500</v>
+      </c>
+      <c r="G37">
+        <v>5200</v>
+      </c>
+      <c r="H37" t="str">
+        <v>Mega Life Sciences</v>
+      </c>
+      <c r="I37" t="str">
+        <v>Consumer Health</v>
+      </c>
+      <c r="J37" t="str">
+        <v>No</v>
+      </c>
+      <c r="K37" t="str">
+        <v>Antacid Gel Suspension 240ml (Aluminum &amp; Magnesium Hydroxide) pharmaceutical grade</v>
+      </c>
+      <c r="L37" t="str">
+        <v>Aluminum &amp; Magnesium Hydroxide</v>
+      </c>
+      <c r="M37" t="str">
+        <v>Gaviscon</v>
+      </c>
+      <c r="N37" t="str">
+        <v>Bottle</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>PRD-037</v>
+      </c>
+      <c r="B38" t="str">
+        <v>SKU-1037</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Hyoscine Butylbromide 10mg</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Gastrointestinal</v>
+      </c>
+      <c r="E38" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F38">
+        <v>3800</v>
+      </c>
+      <c r="G38">
+        <v>5600</v>
+      </c>
+      <c r="H38" t="str">
+        <v>Apex Healthcare</v>
+      </c>
+      <c r="I38" t="str">
+        <v>Consumer Health</v>
+      </c>
+      <c r="J38" t="str">
+        <v>No</v>
+      </c>
+      <c r="K38" t="str">
+        <v>Hyoscine Butylbromide 10mg (Hyoscine Butylbromide) pharmaceutical grade</v>
+      </c>
+      <c r="L38" t="str">
+        <v>Hyoscine Butylbromide</v>
+      </c>
+      <c r="M38" t="str">
+        <v>Buscopan</v>
+      </c>
+      <c r="N38" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>PRD-038</v>
+      </c>
+      <c r="B39" t="str">
+        <v>SKU-1038</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Lactulose Syrup 100ml</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Gastrointestinal</v>
+      </c>
+      <c r="E39" t="str">
+        <v>Bottle</v>
+      </c>
+      <c r="F39">
+        <v>4500</v>
+      </c>
+      <c r="G39">
+        <v>6500</v>
+      </c>
+      <c r="H39" t="str">
+        <v>Apex Healthcare</v>
+      </c>
+      <c r="I39" t="str">
+        <v>Consumer Health</v>
+      </c>
+      <c r="J39" t="str">
+        <v>No</v>
+      </c>
+      <c r="K39" t="str">
+        <v>Lactulose Syrup 100ml (Lactulose) pharmaceutical grade</v>
+      </c>
+      <c r="L39" t="str">
+        <v>Lactulose</v>
+      </c>
+      <c r="M39" t="str">
+        <v>Duphalac</v>
+      </c>
+      <c r="N39" t="str">
+        <v>Bottle</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>PRD-039</v>
+      </c>
+      <c r="B40" t="str">
+        <v>SKU-1039</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Probiotics Complex Capsule</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Gastrointestinal</v>
+      </c>
+      <c r="E40" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F40">
+        <v>9000</v>
+      </c>
+      <c r="G40">
+        <v>13000</v>
+      </c>
+      <c r="H40" t="str">
+        <v>Pacific Health</v>
+      </c>
+      <c r="I40" t="str">
+        <v>Consumer Health</v>
+      </c>
+      <c r="J40" t="str">
+        <v>No</v>
+      </c>
+      <c r="K40" t="str">
+        <v>Probiotics Complex Capsule (Lactobacillus Complex) pharmaceutical grade</v>
+      </c>
+      <c r="L40" t="str">
+        <v>Lactobacillus Complex</v>
+      </c>
+      <c r="M40" t="str">
+        <v>Bio-Flora</v>
+      </c>
+      <c r="N40" t="str">
+        <v>Capsule</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>PRD-040</v>
+      </c>
+      <c r="B41" t="str">
+        <v>SKU-1040</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Amlodipine 5mg</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Cardiovascular</v>
+      </c>
+      <c r="E41" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F41">
+        <v>3000</v>
+      </c>
+      <c r="G41">
+        <v>4500</v>
+      </c>
+      <c r="H41" t="str">
+        <v>Novartis Alliance</v>
+      </c>
+      <c r="I41" t="str">
+        <v>Specialty Pharma</v>
+      </c>
+      <c r="J41" t="str">
+        <v>No</v>
+      </c>
+      <c r="K41" t="str">
+        <v>Amlodipine 5mg (Amlodipine) pharmaceutical grade</v>
+      </c>
+      <c r="L41" t="str">
+        <v>Amlodipine</v>
+      </c>
+      <c r="M41" t="str">
+        <v>Norvasc</v>
+      </c>
+      <c r="N41" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>PRD-041</v>
+      </c>
+      <c r="B42" t="str">
+        <v>SKU-1041</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Amlodipine 10mg</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Cardiovascular</v>
+      </c>
+      <c r="E42" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F42">
+        <v>4500</v>
+      </c>
+      <c r="G42">
+        <v>6500</v>
+      </c>
+      <c r="H42" t="str">
+        <v>Novartis Alliance</v>
+      </c>
+      <c r="I42" t="str">
+        <v>Specialty Pharma</v>
+      </c>
+      <c r="J42" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="K42" t="str">
+        <v>Amlodipine 10mg (Amlodipine) pharmaceutical grade</v>
+      </c>
+      <c r="L42" t="str">
+        <v>Amlodipine</v>
+      </c>
+      <c r="M42" t="str">
+        <v>Norvasc</v>
+      </c>
+      <c r="N42" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>PRD-042</v>
+      </c>
+      <c r="B43" t="str">
+        <v>SKU-1042</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Losartan Potassium 50mg</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Cardiovascular</v>
+      </c>
+      <c r="E43" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F43">
+        <v>4200</v>
+      </c>
+      <c r="G43">
+        <v>6200</v>
+      </c>
+      <c r="H43" t="str">
+        <v>Sun Pharma Group</v>
+      </c>
+      <c r="I43" t="str">
+        <v>Specialty Pharma</v>
+      </c>
+      <c r="J43" t="str">
+        <v>No</v>
+      </c>
+      <c r="K43" t="str">
+        <v>Losartan Potassium 50mg (Losartan) pharmaceutical grade</v>
+      </c>
+      <c r="L43" t="str">
+        <v>Losartan</v>
+      </c>
+      <c r="M43" t="str">
+        <v>Cozaar</v>
+      </c>
+      <c r="N43" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>PRD-043</v>
+      </c>
+      <c r="B44" t="str">
+        <v>SKU-1043</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Telmisartan 40mg</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Cardiovascular</v>
+      </c>
+      <c r="E44" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F44">
+        <v>6800</v>
+      </c>
+      <c r="G44">
+        <v>9800</v>
+      </c>
+      <c r="H44" t="str">
+        <v>Sun Pharma Group</v>
+      </c>
+      <c r="I44" t="str">
+        <v>Specialty Pharma</v>
+      </c>
+      <c r="J44" t="str">
+        <v>No</v>
+      </c>
+      <c r="K44" t="str">
+        <v>Telmisartan 40mg (Telmisartan) pharmaceutical grade</v>
+      </c>
+      <c r="L44" t="str">
+        <v>Telmisartan</v>
+      </c>
+      <c r="M44" t="str">
+        <v>Micardis</v>
+      </c>
+      <c r="N44" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>PRD-044</v>
+      </c>
+      <c r="B45" t="str">
+        <v>SKU-1044</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Telmisartan + Amlodipine (40/5mg)</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Cardiovascular</v>
+      </c>
+      <c r="E45" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F45">
+        <v>11500</v>
+      </c>
+      <c r="G45">
+        <v>16000</v>
+      </c>
+      <c r="H45" t="str">
+        <v>Sun Pharma Group</v>
+      </c>
+      <c r="I45" t="str">
+        <v>Specialty Pharma</v>
+      </c>
+      <c r="J45" t="str">
+        <v>No</v>
+      </c>
+      <c r="K45" t="str">
+        <v>Telmisartan + Amlodipine (40/5mg) (Telmisartan + Amlodipine) pharmaceutical grade</v>
+      </c>
+      <c r="L45" t="str">
+        <v>Telmisartan + Amlodipine</v>
+      </c>
+      <c r="M45" t="str">
+        <v>Twynsta</v>
+      </c>
+      <c r="N45" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>PRD-045</v>
+      </c>
+      <c r="B46" t="str">
+        <v>SKU-1045</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Atorvastatin 20mg</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Cardiovascular</v>
+      </c>
+      <c r="E46" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F46">
+        <v>6500</v>
+      </c>
+      <c r="G46">
+        <v>9500</v>
+      </c>
+      <c r="H46" t="str">
+        <v>Apex Healthcare</v>
+      </c>
+      <c r="I46" t="str">
+        <v>Specialty Pharma</v>
+      </c>
+      <c r="J46" t="str">
+        <v>No</v>
+      </c>
+      <c r="K46" t="str">
+        <v>Atorvastatin 20mg (Atorvastatin) pharmaceutical grade</v>
+      </c>
+      <c r="L46" t="str">
+        <v>Atorvastatin</v>
+      </c>
+      <c r="M46" t="str">
+        <v>Lipitor</v>
+      </c>
+      <c r="N46" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>PRD-046</v>
+      </c>
+      <c r="B47" t="str">
+        <v>SKU-1046</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Rosuvastatin 10mg</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Cardiovascular</v>
+      </c>
+      <c r="E47" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F47">
+        <v>9000</v>
+      </c>
+      <c r="G47">
+        <v>13000</v>
+      </c>
+      <c r="H47" t="str">
+        <v>Apex Healthcare</v>
+      </c>
+      <c r="I47" t="str">
+        <v>Specialty Pharma</v>
+      </c>
+      <c r="J47" t="str">
+        <v>No</v>
+      </c>
+      <c r="K47" t="str">
+        <v>Rosuvastatin 10mg (Rosuvastatin) pharmaceutical grade</v>
+      </c>
+      <c r="L47" t="str">
+        <v>Rosuvastatin</v>
+      </c>
+      <c r="M47" t="str">
+        <v>Crestor</v>
+      </c>
+      <c r="N47" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>PRD-047</v>
+      </c>
+      <c r="B48" t="str">
+        <v>SKU-1047</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Bisoprolol 5mg</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Cardiovascular</v>
+      </c>
+      <c r="E48" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F48">
+        <v>5800</v>
+      </c>
+      <c r="G48">
+        <v>8400</v>
+      </c>
+      <c r="H48" t="str">
+        <v>Novartis Alliance</v>
+      </c>
+      <c r="I48" t="str">
+        <v>Specialty Pharma</v>
+      </c>
+      <c r="J48" t="str">
+        <v>No</v>
+      </c>
+      <c r="K48" t="str">
+        <v>Bisoprolol 5mg (Bisoprolol) pharmaceutical grade</v>
+      </c>
+      <c r="L48" t="str">
+        <v>Bisoprolol</v>
+      </c>
+      <c r="M48" t="str">
+        <v>Concor</v>
+      </c>
+      <c r="N48" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>PRD-048</v>
+      </c>
+      <c r="B49" t="str">
+        <v>SKU-1048</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Clopidogrel 75mg</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Cardiovascular</v>
+      </c>
+      <c r="E49" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F49">
+        <v>7200</v>
+      </c>
+      <c r="G49">
+        <v>10500</v>
+      </c>
+      <c r="H49" t="str">
+        <v>Grand Pharma</v>
+      </c>
+      <c r="I49" t="str">
+        <v>Specialty Pharma</v>
+      </c>
+      <c r="J49" t="str">
+        <v>No</v>
+      </c>
+      <c r="K49" t="str">
+        <v>Clopidogrel 75mg (Clopidogrel) pharmaceutical grade</v>
+      </c>
+      <c r="L49" t="str">
+        <v>Clopidogrel</v>
+      </c>
+      <c r="M49" t="str">
+        <v>Plavix</v>
+      </c>
+      <c r="N49" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>PRD-049</v>
+      </c>
+      <c r="B50" t="str">
+        <v>SKU-1049</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Aspirin Cardio 100mg</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Cardiovascular</v>
+      </c>
+      <c r="E50" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F50">
+        <v>2800</v>
+      </c>
+      <c r="G50">
+        <v>4200</v>
+      </c>
+      <c r="H50" t="str">
+        <v>Novartis Alliance</v>
+      </c>
+      <c r="I50" t="str">
+        <v>Consumer Health</v>
+      </c>
+      <c r="J50" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="K50" t="str">
+        <v>Aspirin Cardio 100mg (Aspirin) pharmaceutical grade</v>
+      </c>
+      <c r="L50" t="str">
+        <v>Aspirin</v>
+      </c>
+      <c r="M50" t="str">
+        <v>Aspirin Protect</v>
+      </c>
+      <c r="N50" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>PRD-050</v>
+      </c>
+      <c r="B51" t="str">
+        <v>SKU-1050</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Furosemide 40mg</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Cardiovascular</v>
+      </c>
+      <c r="E51" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F51">
+        <v>2000</v>
+      </c>
+      <c r="G51">
+        <v>3000</v>
+      </c>
+      <c r="H51" t="str">
+        <v>Alpha Pharma</v>
+      </c>
+      <c r="I51" t="str">
+        <v>Medical</v>
+      </c>
+      <c r="J51" t="str">
+        <v>No</v>
+      </c>
+      <c r="K51" t="str">
+        <v>Furosemide 40mg (Furosemide) pharmaceutical grade</v>
+      </c>
+      <c r="L51" t="str">
+        <v>Furosemide</v>
+      </c>
+      <c r="M51" t="str">
+        <v>Lasix</v>
+      </c>
+      <c r="N51" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>PRD-051</v>
+      </c>
+      <c r="B52" t="str">
+        <v>SKU-1051</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Spironolactone 25mg</v>
+      </c>
+      <c r="D52" t="str">
+        <v>Cardiovascular</v>
+      </c>
+      <c r="E52" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F52">
+        <v>4200</v>
+      </c>
+      <c r="G52">
+        <v>6200</v>
+      </c>
+      <c r="H52" t="str">
+        <v>Alpha Pharma</v>
+      </c>
+      <c r="I52" t="str">
+        <v>Medical</v>
+      </c>
+      <c r="J52" t="str">
+        <v>No</v>
+      </c>
+      <c r="K52" t="str">
+        <v>Spironolactone 25mg (Spironolactone) pharmaceutical grade</v>
+      </c>
+      <c r="L52" t="str">
+        <v>Spironolactone</v>
+      </c>
+      <c r="M52" t="str">
+        <v>Aldactone</v>
+      </c>
+      <c r="N52" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>PRD-052</v>
+      </c>
+      <c r="B53" t="str">
+        <v>SKU-1052</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Cetirizine 10mg</v>
+      </c>
+      <c r="D53" t="str">
+        <v>Respiratory</v>
+      </c>
+      <c r="E53" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F53">
+        <v>2200</v>
+      </c>
+      <c r="G53">
+        <v>3400</v>
+      </c>
+      <c r="H53" t="str">
+        <v>Mega Life Sciences</v>
+      </c>
+      <c r="I53" t="str">
+        <v>Consumer Health</v>
+      </c>
+      <c r="J53" t="str">
+        <v>No</v>
+      </c>
+      <c r="K53" t="str">
+        <v>Cetirizine 10mg (Cetirizine) pharmaceutical grade</v>
+      </c>
+      <c r="L53" t="str">
+        <v>Cetirizine</v>
+      </c>
+      <c r="M53" t="str">
+        <v>Zyrtec</v>
+      </c>
+      <c r="N53" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>PRD-053</v>
+      </c>
+      <c r="B54" t="str">
+        <v>SKU-1053</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Loratadine 10mg</v>
+      </c>
+      <c r="D54" t="str">
+        <v>Respiratory</v>
+      </c>
+      <c r="E54" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F54">
+        <v>2600</v>
+      </c>
+      <c r="G54">
+        <v>3900</v>
+      </c>
+      <c r="H54" t="str">
+        <v>Mega Life Sciences</v>
+      </c>
+      <c r="I54" t="str">
+        <v>Consumer Health</v>
+      </c>
+      <c r="J54" t="str">
+        <v>No</v>
+      </c>
+      <c r="K54" t="str">
+        <v>Loratadine 10mg (Loratadine) pharmaceutical grade</v>
+      </c>
+      <c r="L54" t="str">
+        <v>Loratadine</v>
+      </c>
+      <c r="M54" t="str">
+        <v>Claritin</v>
+      </c>
+      <c r="N54" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>PRD-054</v>
+      </c>
+      <c r="B55" t="str">
+        <v>SKU-1054</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Fexofenadine 180mg</v>
+      </c>
+      <c r="D55" t="str">
+        <v>Respiratory</v>
+      </c>
+      <c r="E55" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F55">
+        <v>8500</v>
+      </c>
+      <c r="G55">
+        <v>12500</v>
+      </c>
+      <c r="H55" t="str">
+        <v>Apex Healthcare</v>
+      </c>
+      <c r="I55" t="str">
+        <v>Medical</v>
+      </c>
+      <c r="J55" t="str">
+        <v>No</v>
+      </c>
+      <c r="K55" t="str">
+        <v>Fexofenadine 180mg (Fexofenadine) pharmaceutical grade</v>
+      </c>
+      <c r="L55" t="str">
+        <v>Fexofenadine</v>
+      </c>
+      <c r="M55" t="str">
+        <v>Telfast</v>
+      </c>
+      <c r="N55" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>PRD-055</v>
+      </c>
+      <c r="B56" t="str">
+        <v>SKU-1055</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Montelukast 10mg</v>
+      </c>
+      <c r="D56" t="str">
+        <v>Respiratory</v>
+      </c>
+      <c r="E56" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F56">
+        <v>9500</v>
+      </c>
+      <c r="G56">
+        <v>14000</v>
+      </c>
+      <c r="H56" t="str">
+        <v>Apex Healthcare</v>
+      </c>
+      <c r="I56" t="str">
+        <v>Specialty Pharma</v>
+      </c>
+      <c r="J56" t="str">
+        <v>No</v>
+      </c>
+      <c r="K56" t="str">
+        <v>Montelukast 10mg (Montelukast) pharmaceutical grade</v>
+      </c>
+      <c r="L56" t="str">
+        <v>Montelukast</v>
+      </c>
+      <c r="M56" t="str">
+        <v>Singulair</v>
+      </c>
+      <c r="N56" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>PRD-056</v>
+      </c>
+      <c r="B57" t="str">
+        <v>SKU-1056</v>
+      </c>
+      <c r="C57" t="str">
+        <v>Salbutamol Inhaler 100mcg</v>
+      </c>
+      <c r="D57" t="str">
+        <v>Respiratory</v>
+      </c>
+      <c r="E57" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F57">
+        <v>7500</v>
+      </c>
+      <c r="G57">
+        <v>11000</v>
+      </c>
+      <c r="H57" t="str">
+        <v>Apex Healthcare</v>
+      </c>
+      <c r="I57" t="str">
+        <v>Medical</v>
+      </c>
+      <c r="J57" t="str">
+        <v>No</v>
+      </c>
+      <c r="K57" t="str">
+        <v>Salbutamol Inhaler 100mcg (Salbutamol) pharmaceutical grade</v>
+      </c>
+      <c r="L57" t="str">
+        <v>Salbutamol</v>
+      </c>
+      <c r="M57" t="str">
+        <v>Ventolin Inhaler</v>
+      </c>
+      <c r="N57" t="str">
+        <v>Inhaler</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>PRD-057</v>
+      </c>
+      <c r="B58" t="str">
+        <v>SKU-1057</v>
+      </c>
+      <c r="C58" t="str">
+        <v>Seretide Inhaler 25/125mcg</v>
+      </c>
+      <c r="D58" t="str">
+        <v>Respiratory</v>
+      </c>
+      <c r="E58" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F58">
+        <v>26000</v>
+      </c>
+      <c r="G58">
+        <v>35000</v>
+      </c>
+      <c r="H58" t="str">
+        <v>Apex Healthcare</v>
+      </c>
+      <c r="I58" t="str">
+        <v>Specialty Pharma</v>
+      </c>
+      <c r="J58" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="K58" t="str">
+        <v>Seretide Inhaler 25/125mcg (Salmeterol + Fluticasone) pharmaceutical grade</v>
+      </c>
+      <c r="L58" t="str">
+        <v>Salmeterol + Fluticasone</v>
+      </c>
+      <c r="M58" t="str">
+        <v>Seretide Evohaler</v>
+      </c>
+      <c r="N58" t="str">
+        <v>Inhaler</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>PRD-058</v>
+      </c>
+      <c r="B59" t="str">
+        <v>SKU-1058</v>
+      </c>
+      <c r="C59" t="str">
+        <v>Dextromethorphan Syrup 60ml</v>
+      </c>
+      <c r="D59" t="str">
+        <v>Respiratory</v>
+      </c>
+      <c r="E59" t="str">
+        <v>Bottle</v>
+      </c>
+      <c r="F59">
+        <v>2400</v>
+      </c>
+      <c r="G59">
+        <v>3600</v>
+      </c>
+      <c r="H59" t="str">
+        <v>Mega Life Sciences</v>
+      </c>
+      <c r="I59" t="str">
+        <v>Consumer Health</v>
+      </c>
+      <c r="J59" t="str">
+        <v>No</v>
+      </c>
+      <c r="K59" t="str">
+        <v>Dextromethorphan Syrup 60ml (Dextromethorphan) pharmaceutical grade</v>
+      </c>
+      <c r="L59" t="str">
+        <v>Dextromethorphan</v>
+      </c>
+      <c r="M59" t="str">
+        <v>Bisolvon Dry</v>
+      </c>
+      <c r="N59" t="str">
+        <v>Bottle</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>PRD-059</v>
+      </c>
+      <c r="B60" t="str">
+        <v>SKU-1059</v>
+      </c>
+      <c r="C60" t="str">
+        <v>Bromhexine 8mg</v>
+      </c>
+      <c r="D60" t="str">
+        <v>Respiratory</v>
+      </c>
+      <c r="E60" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F60">
+        <v>1800</v>
+      </c>
+      <c r="G60">
+        <v>2700</v>
+      </c>
+      <c r="H60" t="str">
+        <v>Mega Life Sciences</v>
+      </c>
+      <c r="I60" t="str">
+        <v>Consumer Health</v>
+      </c>
+      <c r="J60" t="str">
+        <v>No</v>
+      </c>
+      <c r="K60" t="str">
+        <v>Bromhexine 8mg (Bromhexine) pharmaceutical grade</v>
+      </c>
+      <c r="L60" t="str">
+        <v>Bromhexine</v>
+      </c>
+      <c r="M60" t="str">
+        <v>Bisolvon</v>
+      </c>
+      <c r="N60" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>PRD-060</v>
+      </c>
+      <c r="B61" t="str">
+        <v>SKU-1060</v>
+      </c>
+      <c r="C61" t="str">
+        <v>Acetylcysteine 600mg Effervescent</v>
+      </c>
+      <c r="D61" t="str">
+        <v>Respiratory</v>
+      </c>
+      <c r="E61" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F61">
+        <v>8800</v>
+      </c>
+      <c r="G61">
+        <v>12800</v>
+      </c>
+      <c r="H61" t="str">
+        <v>Pacific Health</v>
+      </c>
+      <c r="I61" t="str">
+        <v>Consumer Health</v>
+      </c>
+      <c r="J61" t="str">
+        <v>No</v>
+      </c>
+      <c r="K61" t="str">
+        <v>Acetylcysteine 600mg Effervescent (N-Acetylcysteine) pharmaceutical grade</v>
+      </c>
+      <c r="L61" t="str">
+        <v>N-Acetylcysteine</v>
+      </c>
+      <c r="M61" t="str">
+        <v>Fluimucil</v>
+      </c>
+      <c r="N61" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>PRD-061</v>
+      </c>
+      <c r="B62" t="str">
+        <v>SKU-1061</v>
+      </c>
+      <c r="C62" t="str">
+        <v>Fluticasone Nasal Spray</v>
+      </c>
+      <c r="D62" t="str">
+        <v>Respiratory</v>
+      </c>
+      <c r="E62" t="str">
+        <v>Bottle</v>
+      </c>
+      <c r="F62">
+        <v>14000</v>
+      </c>
+      <c r="G62">
+        <v>19500</v>
+      </c>
+      <c r="H62" t="str">
+        <v>Apex Healthcare</v>
+      </c>
+      <c r="I62" t="str">
+        <v>Specialty Pharma</v>
+      </c>
+      <c r="J62" t="str">
+        <v>No</v>
+      </c>
+      <c r="K62" t="str">
+        <v>Fluticasone Nasal Spray (Fluticasone Propionate) pharmaceutical grade</v>
+      </c>
+      <c r="L62" t="str">
+        <v>Fluticasone Propionate</v>
+      </c>
+      <c r="M62" t="str">
+        <v>Flixonase</v>
+      </c>
+      <c r="N62" t="str">
+        <v>Bottle</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>PRD-062</v>
+      </c>
+      <c r="B63" t="str">
+        <v>SKU-1062</v>
+      </c>
+      <c r="C63" t="str">
+        <v>Vitamin C 500mg Chewable</v>
+      </c>
+      <c r="D63" t="str">
+        <v>Vitamins &amp; Minerals</v>
+      </c>
+      <c r="E63" t="str">
+        <v>Bottle</v>
+      </c>
+      <c r="F63">
+        <v>3000</v>
+      </c>
+      <c r="G63">
+        <v>4500</v>
+      </c>
+      <c r="H63" t="str">
+        <v>Mega Life Sciences</v>
+      </c>
+      <c r="I63" t="str">
+        <v>Consumer Health</v>
+      </c>
+      <c r="J63" t="str">
+        <v>No</v>
+      </c>
+      <c r="K63" t="str">
+        <v>Vitamin C 500mg Chewable (Ascorbic Acid) pharmaceutical grade</v>
+      </c>
+      <c r="L63" t="str">
+        <v>Ascorbic Acid</v>
+      </c>
+      <c r="M63" t="str">
+        <v>C-Viton</v>
+      </c>
+      <c r="N63" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>PRD-063</v>
+      </c>
+      <c r="B64" t="str">
+        <v>SKU-1063</v>
+      </c>
+      <c r="C64" t="str">
+        <v>Vitamin B-Complex High Potency</v>
+      </c>
+      <c r="D64" t="str">
+        <v>Vitamins &amp; Minerals</v>
+      </c>
+      <c r="E64" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F64">
+        <v>5200</v>
+      </c>
+      <c r="G64">
+        <v>7800</v>
+      </c>
+      <c r="H64" t="str">
+        <v>Mega Life Sciences</v>
+      </c>
+      <c r="I64" t="str">
+        <v>Consumer Health</v>
+      </c>
+      <c r="J64" t="str">
+        <v>No</v>
+      </c>
+      <c r="K64" t="str">
+        <v>Vitamin B-Complex High Potency (Vitamin B1+B6+B12) pharmaceutical grade</v>
+      </c>
+      <c r="L64" t="str">
+        <v>Vitamin B1+B6+B12</v>
+      </c>
+      <c r="M64" t="str">
+        <v>Neurobion</v>
+      </c>
+      <c r="N64" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>PRD-064</v>
+      </c>
+      <c r="B65" t="str">
+        <v>SKU-1064</v>
+      </c>
+      <c r="C65" t="str">
+        <v>Calcium + Vitamin D3 600mg</v>
+      </c>
+      <c r="D65" t="str">
+        <v>Vitamins &amp; Minerals</v>
+      </c>
+      <c r="E65" t="str">
+        <v>Bottle</v>
+      </c>
+      <c r="F65">
+        <v>6500</v>
+      </c>
+      <c r="G65">
+        <v>9500</v>
+      </c>
+      <c r="H65" t="str">
+        <v>Pacific Health</v>
+      </c>
+      <c r="I65" t="str">
+        <v>Consumer Health</v>
+      </c>
+      <c r="J65" t="str">
+        <v>No</v>
+      </c>
+      <c r="K65" t="str">
+        <v>Calcium + Vitamin D3 600mg (Calcium Carbonate + D3) pharmaceutical grade</v>
+      </c>
+      <c r="L65" t="str">
+        <v>Calcium Carbonate + D3</v>
+      </c>
+      <c r="M65" t="str">
+        <v>Caltrate Plus</v>
+      </c>
+      <c r="N65" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>PRD-065</v>
+      </c>
+      <c r="B66" t="str">
+        <v>SKU-1065</v>
+      </c>
+      <c r="C66" t="str">
+        <v>Multivitamins &amp; Minerals with Ginseng</v>
+      </c>
+      <c r="D66" t="str">
+        <v>Vitamins &amp; Minerals</v>
+      </c>
+      <c r="E66" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F66">
+        <v>12500</v>
+      </c>
+      <c r="G66">
+        <v>17500</v>
+      </c>
+      <c r="H66" t="str">
+        <v>Pacific Health</v>
+      </c>
+      <c r="I66" t="str">
+        <v>Consumer Health</v>
+      </c>
+      <c r="J66" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="K66" t="str">
+        <v>Multivitamins &amp; Minerals with Ginseng (Multivitamin Formula) pharmaceutical grade</v>
+      </c>
+      <c r="L66" t="str">
+        <v>Multivitamin Formula</v>
+      </c>
+      <c r="M66" t="str">
+        <v>Pharmaton G115</v>
+      </c>
+      <c r="N66" t="str">
+        <v>Capsule</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>PRD-066</v>
+      </c>
+      <c r="B67" t="str">
+        <v>SKU-1066</v>
+      </c>
+      <c r="C67" t="str">
+        <v>Omega-3 Fish Oil 1000mg</v>
+      </c>
+      <c r="D67" t="str">
+        <v>Vitamins &amp; Minerals</v>
+      </c>
+      <c r="E67" t="str">
+        <v>Bottle</v>
+      </c>
+      <c r="F67">
+        <v>11000</v>
+      </c>
+      <c r="G67">
+        <v>15800</v>
+      </c>
+      <c r="H67" t="str">
+        <v>Pacific Health</v>
+      </c>
+      <c r="I67" t="str">
+        <v>Consumer Health</v>
+      </c>
+      <c r="J67" t="str">
+        <v>No</v>
+      </c>
+      <c r="K67" t="str">
+        <v>Omega-3 Fish Oil 1000mg (Fish Oil EPA/DHA) pharmaceutical grade</v>
+      </c>
+      <c r="L67" t="str">
+        <v>Fish Oil EPA/DHA</v>
+      </c>
+      <c r="M67" t="str">
+        <v>Blackmores Omega-3</v>
+      </c>
+      <c r="N67" t="str">
+        <v>Capsule</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>PRD-067</v>
+      </c>
+      <c r="B68" t="str">
+        <v>SKU-1067</v>
+      </c>
+      <c r="C68" t="str">
+        <v>Iron + Folic Acid Complex</v>
+      </c>
+      <c r="D68" t="str">
+        <v>Vitamins &amp; Minerals</v>
+      </c>
+      <c r="E68" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F68">
+        <v>4800</v>
+      </c>
+      <c r="G68">
+        <v>7200</v>
+      </c>
+      <c r="H68" t="str">
+        <v>Mega Life Sciences</v>
+      </c>
+      <c r="I68" t="str">
+        <v>Consumer Health</v>
+      </c>
+      <c r="J68" t="str">
+        <v>No</v>
+      </c>
+      <c r="K68" t="str">
+        <v>Iron + Folic Acid Complex (Ferrous Fumarate + Folic Acid) pharmaceutical grade</v>
+      </c>
+      <c r="L68" t="str">
+        <v>Ferrous Fumarate + Folic Acid</v>
+      </c>
+      <c r="M68" t="str">
+        <v>Iberet Folic</v>
+      </c>
+      <c r="N68" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>PRD-068</v>
+      </c>
+      <c r="B69" t="str">
+        <v>SKU-1068</v>
+      </c>
+      <c r="C69" t="str">
+        <v>Zinc 50mg Tablets</v>
+      </c>
+      <c r="D69" t="str">
+        <v>Vitamins &amp; Minerals</v>
+      </c>
+      <c r="E69" t="str">
+        <v>Bottle</v>
+      </c>
+      <c r="F69">
+        <v>3500</v>
+      </c>
+      <c r="G69">
+        <v>5200</v>
+      </c>
+      <c r="H69" t="str">
+        <v>Mega Life Sciences</v>
+      </c>
+      <c r="I69" t="str">
+        <v>Consumer Health</v>
+      </c>
+      <c r="J69" t="str">
+        <v>No</v>
+      </c>
+      <c r="K69" t="str">
+        <v>Zinc 50mg Tablets (Zinc Gluconate) pharmaceutical grade</v>
+      </c>
+      <c r="L69" t="str">
+        <v>Zinc Gluconate</v>
+      </c>
+      <c r="M69" t="str">
+        <v>Zinc-Life</v>
+      </c>
+      <c r="N69" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>PRD-069</v>
+      </c>
+      <c r="B70" t="str">
+        <v>SKU-1069</v>
+      </c>
+      <c r="C70" t="str">
+        <v>Vitamin D3 2000 IU</v>
+      </c>
+      <c r="D70" t="str">
+        <v>Vitamins &amp; Minerals</v>
+      </c>
+      <c r="E70" t="str">
+        <v>Bottle</v>
+      </c>
+      <c r="F70">
+        <v>7200</v>
+      </c>
+      <c r="G70">
+        <v>10500</v>
+      </c>
+      <c r="H70" t="str">
+        <v>Pacific Health</v>
+      </c>
+      <c r="I70" t="str">
+        <v>Consumer Health</v>
+      </c>
+      <c r="J70" t="str">
+        <v>No</v>
+      </c>
+      <c r="K70" t="str">
+        <v>Vitamin D3 2000 IU (Cholecalciferol) pharmaceutical grade</v>
+      </c>
+      <c r="L70" t="str">
+        <v>Cholecalciferol</v>
+      </c>
+      <c r="M70" t="str">
+        <v>D3-Max</v>
+      </c>
+      <c r="N70" t="str">
+        <v>Capsule</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>PRD-070</v>
+      </c>
+      <c r="B71" t="str">
+        <v>SKU-1070</v>
+      </c>
+      <c r="C71" t="str">
+        <v>Glucosamine &amp; Chondroitin 1500mg</v>
+      </c>
+      <c r="D71" t="str">
+        <v>Vitamins &amp; Minerals</v>
+      </c>
+      <c r="E71" t="str">
+        <v>Bottle</v>
+      </c>
+      <c r="F71">
+        <v>16000</v>
+      </c>
+      <c r="G71">
+        <v>23000</v>
+      </c>
+      <c r="H71" t="str">
+        <v>Pacific Health</v>
+      </c>
+      <c r="I71" t="str">
+        <v>Consumer Health</v>
+      </c>
+      <c r="J71" t="str">
+        <v>No</v>
+      </c>
+      <c r="K71" t="str">
+        <v>Glucosamine &amp; Chondroitin 1500mg (Glucosamine Sulfate) pharmaceutical grade</v>
+      </c>
+      <c r="L71" t="str">
+        <v>Glucosamine Sulfate</v>
+      </c>
+      <c r="M71" t="str">
+        <v>Joint-Flex</v>
+      </c>
+      <c r="N71" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>PRD-071</v>
+      </c>
+      <c r="B72" t="str">
+        <v>SKU-1071</v>
+      </c>
+      <c r="C72" t="str">
+        <v>Coenzyme Q10 100mg</v>
+      </c>
+      <c r="D72" t="str">
+        <v>Vitamins &amp; Minerals</v>
+      </c>
+      <c r="E72" t="str">
+        <v>Bottle</v>
+      </c>
+      <c r="F72">
+        <v>18000</v>
+      </c>
+      <c r="G72">
+        <v>25500</v>
+      </c>
+      <c r="H72" t="str">
+        <v>Pacific Health</v>
+      </c>
+      <c r="I72" t="str">
+        <v>Consumer Health</v>
+      </c>
+      <c r="J72" t="str">
+        <v>No</v>
+      </c>
+      <c r="K72" t="str">
+        <v>Coenzyme Q10 100mg (Coenzyme Q10) pharmaceutical grade</v>
+      </c>
+      <c r="L72" t="str">
+        <v>Coenzyme Q10</v>
+      </c>
+      <c r="M72" t="str">
+        <v>CoQ-Vital</v>
+      </c>
+      <c r="N72" t="str">
+        <v>Capsule</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>PRD-072</v>
+      </c>
+      <c r="B73" t="str">
+        <v>SKU-1072</v>
+      </c>
+      <c r="C73" t="str">
+        <v>Metformin 500mg</v>
+      </c>
+      <c r="D73" t="str">
+        <v>Antidiabetic</v>
+      </c>
+      <c r="E73" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F73">
+        <v>2500</v>
+      </c>
+      <c r="G73">
+        <v>3800</v>
+      </c>
+      <c r="H73" t="str">
+        <v>Sun Pharma Group</v>
+      </c>
+      <c r="I73" t="str">
+        <v>Medical</v>
+      </c>
+      <c r="J73" t="str">
+        <v>No</v>
+      </c>
+      <c r="K73" t="str">
+        <v>Metformin 500mg (Metformin HCl) pharmaceutical grade</v>
+      </c>
+      <c r="L73" t="str">
+        <v>Metformin HCl</v>
+      </c>
+      <c r="M73" t="str">
+        <v>Glucophage</v>
+      </c>
+      <c r="N73" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>PRD-073</v>
+      </c>
+      <c r="B74" t="str">
+        <v>SKU-1073</v>
+      </c>
+      <c r="C74" t="str">
+        <v>Metformin 850mg XR</v>
+      </c>
+      <c r="D74" t="str">
+        <v>Antidiabetic</v>
+      </c>
+      <c r="E74" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F74">
+        <v>4200</v>
+      </c>
+      <c r="G74">
+        <v>6200</v>
+      </c>
+      <c r="H74" t="str">
+        <v>Sun Pharma Group</v>
+      </c>
+      <c r="I74" t="str">
+        <v>Medical</v>
+      </c>
+      <c r="J74" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="K74" t="str">
+        <v>Metformin 850mg XR (Metformin Extended Release) pharmaceutical grade</v>
+      </c>
+      <c r="L74" t="str">
+        <v>Metformin Extended Release</v>
+      </c>
+      <c r="M74" t="str">
+        <v>Glucophage XR</v>
+      </c>
+      <c r="N74" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>PRD-074</v>
+      </c>
+      <c r="B75" t="str">
+        <v>SKU-1074</v>
+      </c>
+      <c r="C75" t="str">
+        <v>Gliclazide 80mg</v>
+      </c>
+      <c r="D75" t="str">
+        <v>Antidiabetic</v>
+      </c>
+      <c r="E75" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F75">
+        <v>4800</v>
+      </c>
+      <c r="G75">
+        <v>7000</v>
+      </c>
+      <c r="H75" t="str">
+        <v>Sun Pharma Group</v>
+      </c>
+      <c r="I75" t="str">
+        <v>Medical</v>
+      </c>
+      <c r="J75" t="str">
+        <v>No</v>
+      </c>
+      <c r="K75" t="str">
+        <v>Gliclazide 80mg (Gliclazide) pharmaceutical grade</v>
+      </c>
+      <c r="L75" t="str">
+        <v>Gliclazide</v>
+      </c>
+      <c r="M75" t="str">
+        <v>Diamicron</v>
+      </c>
+      <c r="N75" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>PRD-075</v>
+      </c>
+      <c r="B76" t="str">
+        <v>SKU-1075</v>
+      </c>
+      <c r="C76" t="str">
+        <v>Glimepiride 2mg</v>
+      </c>
+      <c r="D76" t="str">
+        <v>Antidiabetic</v>
+      </c>
+      <c r="E76" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F76">
+        <v>3600</v>
+      </c>
+      <c r="G76">
+        <v>5400</v>
+      </c>
+      <c r="H76" t="str">
+        <v>Sun Pharma Group</v>
+      </c>
+      <c r="I76" t="str">
+        <v>Medical</v>
+      </c>
+      <c r="J76" t="str">
+        <v>No</v>
+      </c>
+      <c r="K76" t="str">
+        <v>Glimepiride 2mg (Glimepiride) pharmaceutical grade</v>
+      </c>
+      <c r="L76" t="str">
+        <v>Glimepiride</v>
+      </c>
+      <c r="M76" t="str">
+        <v>Amaryl</v>
+      </c>
+      <c r="N76" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>PRD-076</v>
+      </c>
+      <c r="B77" t="str">
+        <v>SKU-1076</v>
+      </c>
+      <c r="C77" t="str">
+        <v>Sitagliptin 100mg</v>
+      </c>
+      <c r="D77" t="str">
+        <v>Antidiabetic</v>
+      </c>
+      <c r="E77" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F77">
+        <v>21000</v>
+      </c>
+      <c r="G77">
+        <v>28500</v>
+      </c>
+      <c r="H77" t="str">
+        <v>Novartis Alliance</v>
+      </c>
+      <c r="I77" t="str">
+        <v>Specialty Pharma</v>
+      </c>
+      <c r="J77" t="str">
+        <v>No</v>
+      </c>
+      <c r="K77" t="str">
+        <v>Sitagliptin 100mg (Sitagliptin) pharmaceutical grade</v>
+      </c>
+      <c r="L77" t="str">
+        <v>Sitagliptin</v>
+      </c>
+      <c r="M77" t="str">
+        <v>Januvia</v>
+      </c>
+      <c r="N77" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>PRD-077</v>
+      </c>
+      <c r="B78" t="str">
+        <v>SKU-1077</v>
+      </c>
+      <c r="C78" t="str">
+        <v>Empagliflozin 10mg</v>
+      </c>
+      <c r="D78" t="str">
+        <v>Antidiabetic</v>
+      </c>
+      <c r="E78" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F78">
+        <v>24000</v>
+      </c>
+      <c r="G78">
+        <v>32000</v>
+      </c>
+      <c r="H78" t="str">
+        <v>Novartis Alliance</v>
+      </c>
+      <c r="I78" t="str">
+        <v>Specialty Pharma</v>
+      </c>
+      <c r="J78" t="str">
+        <v>No</v>
+      </c>
+      <c r="K78" t="str">
+        <v>Empagliflozin 10mg (Empagliflozin) pharmaceutical grade</v>
+      </c>
+      <c r="L78" t="str">
+        <v>Empagliflozin</v>
+      </c>
+      <c r="M78" t="str">
+        <v>Jardiance</v>
+      </c>
+      <c r="N78" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>PRD-078</v>
+      </c>
+      <c r="B79" t="str">
+        <v>SKU-1078</v>
+      </c>
+      <c r="C79" t="str">
+        <v>Dapagliflozin 10mg</v>
+      </c>
+      <c r="D79" t="str">
+        <v>Antidiabetic</v>
+      </c>
+      <c r="E79" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F79">
+        <v>25000</v>
+      </c>
+      <c r="G79">
+        <v>33500</v>
+      </c>
+      <c r="H79" t="str">
+        <v>Novartis Alliance</v>
+      </c>
+      <c r="I79" t="str">
+        <v>Specialty Pharma</v>
+      </c>
+      <c r="J79" t="str">
+        <v>No</v>
+      </c>
+      <c r="K79" t="str">
+        <v>Dapagliflozin 10mg (Dapagliflozin) pharmaceutical grade</v>
+      </c>
+      <c r="L79" t="str">
+        <v>Dapagliflozin</v>
+      </c>
+      <c r="M79" t="str">
+        <v>Forxiga</v>
+      </c>
+      <c r="N79" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>PRD-079</v>
+      </c>
+      <c r="B80" t="str">
+        <v>SKU-1079</v>
+      </c>
+      <c r="C80" t="str">
+        <v>Vildagliptin + Metformin (50/500mg)</v>
+      </c>
+      <c r="D80" t="str">
+        <v>Antidiabetic</v>
+      </c>
+      <c r="E80" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F80">
+        <v>19500</v>
+      </c>
+      <c r="G80">
+        <v>26500</v>
+      </c>
+      <c r="H80" t="str">
+        <v>Novartis Alliance</v>
+      </c>
+      <c r="I80" t="str">
+        <v>Specialty Pharma</v>
+      </c>
+      <c r="J80" t="str">
+        <v>No</v>
+      </c>
+      <c r="K80" t="str">
+        <v>Vildagliptin + Metformin (50/500mg) (Vildagliptin + Metformin) pharmaceutical grade</v>
+      </c>
+      <c r="L80" t="str">
+        <v>Vildagliptin + Metformin</v>
+      </c>
+      <c r="M80" t="str">
+        <v>Galvus Met</v>
+      </c>
+      <c r="N80" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>PRD-080</v>
+      </c>
+      <c r="B81" t="str">
+        <v>SKU-1080</v>
+      </c>
+      <c r="C81" t="str">
+        <v>Hydrocortisone 1% Cream 15g</v>
+      </c>
+      <c r="D81" t="str">
+        <v>Dermatology</v>
+      </c>
+      <c r="E81" t="str">
+        <v>Tube</v>
+      </c>
+      <c r="F81">
+        <v>2000</v>
+      </c>
+      <c r="G81">
+        <v>3000</v>
+      </c>
+      <c r="H81" t="str">
+        <v>Alpha Pharma</v>
+      </c>
+      <c r="I81" t="str">
+        <v>Consumer Health</v>
+      </c>
+      <c r="J81" t="str">
+        <v>No</v>
+      </c>
+      <c r="K81" t="str">
+        <v>Hydrocortisone 1% Cream 15g (Hydrocortisone) pharmaceutical grade</v>
+      </c>
+      <c r="L81" t="str">
+        <v>Hydrocortisone</v>
+      </c>
+      <c r="M81" t="str">
+        <v>Cortaid</v>
+      </c>
+      <c r="N81" t="str">
+        <v>Cream</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>PRD-081</v>
+      </c>
+      <c r="B82" t="str">
+        <v>SKU-1081</v>
+      </c>
+      <c r="C82" t="str">
+        <v>Betamethasone Dipropionate 15g</v>
+      </c>
+      <c r="D82" t="str">
+        <v>Dermatology</v>
+      </c>
+      <c r="E82" t="str">
+        <v>Tube</v>
+      </c>
+      <c r="F82">
+        <v>2800</v>
+      </c>
+      <c r="G82">
+        <v>4200</v>
+      </c>
+      <c r="H82" t="str">
+        <v>Alpha Pharma</v>
+      </c>
+      <c r="I82" t="str">
+        <v>Medical</v>
+      </c>
+      <c r="J82" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="K82" t="str">
+        <v>Betamethasone Dipropionate 15g (Betamethasone) pharmaceutical grade</v>
+      </c>
+      <c r="L82" t="str">
+        <v>Betamethasone</v>
+      </c>
+      <c r="M82" t="str">
+        <v>Diprosone</v>
+      </c>
+      <c r="N82" t="str">
+        <v>Cream</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>PRD-082</v>
+      </c>
+      <c r="B83" t="str">
+        <v>SKU-1082</v>
+      </c>
+      <c r="C83" t="str">
+        <v>Clotrimazole 1% Cream 20g</v>
+      </c>
+      <c r="D83" t="str">
+        <v>Dermatology</v>
+      </c>
+      <c r="E83" t="str">
+        <v>Tube</v>
+      </c>
+      <c r="F83">
+        <v>2500</v>
+      </c>
+      <c r="G83">
+        <v>3800</v>
+      </c>
+      <c r="H83" t="str">
+        <v>Mega Life Sciences</v>
+      </c>
+      <c r="I83" t="str">
+        <v>Consumer Health</v>
+      </c>
+      <c r="J83" t="str">
+        <v>No</v>
+      </c>
+      <c r="K83" t="str">
+        <v>Clotrimazole 1% Cream 20g (Clotrimazole) pharmaceutical grade</v>
+      </c>
+      <c r="L83" t="str">
+        <v>Clotrimazole</v>
+      </c>
+      <c r="M83" t="str">
+        <v>Canesten</v>
+      </c>
+      <c r="N83" t="str">
+        <v>Cream</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>PRD-083</v>
+      </c>
+      <c r="B84" t="str">
+        <v>SKU-1083</v>
+      </c>
+      <c r="C84" t="str">
+        <v>Mupirocin 2% Ointment 5g</v>
+      </c>
+      <c r="D84" t="str">
+        <v>Dermatology</v>
+      </c>
+      <c r="E84" t="str">
+        <v>Tube</v>
+      </c>
+      <c r="F84">
+        <v>3800</v>
+      </c>
+      <c r="G84">
+        <v>5600</v>
+      </c>
+      <c r="H84" t="str">
+        <v>Apex Healthcare</v>
+      </c>
+      <c r="I84" t="str">
+        <v>Medical</v>
+      </c>
+      <c r="J84" t="str">
+        <v>No</v>
+      </c>
+      <c r="K84" t="str">
+        <v>Mupirocin 2% Ointment 5g (Mupirocin) pharmaceutical grade</v>
+      </c>
+      <c r="L84" t="str">
+        <v>Mupirocin</v>
+      </c>
+      <c r="M84" t="str">
+        <v>Bactroban</v>
+      </c>
+      <c r="N84" t="str">
+        <v>Ointment</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>PRD-084</v>
+      </c>
+      <c r="B85" t="str">
+        <v>SKU-1084</v>
+      </c>
+      <c r="C85" t="str">
+        <v>Fusidic Acid Cream 15g</v>
+      </c>
+      <c r="D85" t="str">
+        <v>Dermatology</v>
+      </c>
+      <c r="E85" t="str">
+        <v>Tube</v>
+      </c>
+      <c r="F85">
+        <v>4500</v>
+      </c>
+      <c r="G85">
+        <v>6800</v>
+      </c>
+      <c r="H85" t="str">
+        <v>Apex Healthcare</v>
+      </c>
+      <c r="I85" t="str">
+        <v>Medical</v>
+      </c>
+      <c r="J85" t="str">
+        <v>No</v>
+      </c>
+      <c r="K85" t="str">
+        <v>Fusidic Acid Cream 15g (Fusidic Acid) pharmaceutical grade</v>
+      </c>
+      <c r="L85" t="str">
+        <v>Fusidic Acid</v>
+      </c>
+      <c r="M85" t="str">
+        <v>Fucidin</v>
+      </c>
+      <c r="N85" t="str">
+        <v>Cream</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>PRD-085</v>
+      </c>
+      <c r="B86" t="str">
+        <v>SKU-1085</v>
+      </c>
+      <c r="C86" t="str">
+        <v>Ketoconazole 2% Shampoo 100ml</v>
+      </c>
+      <c r="D86" t="str">
+        <v>Dermatology</v>
+      </c>
+      <c r="E86" t="str">
+        <v>Bottle</v>
+      </c>
+      <c r="F86">
+        <v>5500</v>
+      </c>
+      <c r="G86">
+        <v>8000</v>
+      </c>
+      <c r="H86" t="str">
+        <v>Mega Life Sciences</v>
+      </c>
+      <c r="I86" t="str">
+        <v>Consumer Health</v>
+      </c>
+      <c r="J86" t="str">
+        <v>No</v>
+      </c>
+      <c r="K86" t="str">
+        <v>Ketoconazole 2% Shampoo 100ml (Ketoconazole) pharmaceutical grade</v>
+      </c>
+      <c r="L86" t="str">
+        <v>Ketoconazole</v>
+      </c>
+      <c r="M86" t="str">
+        <v>Nizoral</v>
+      </c>
+      <c r="N86" t="str">
+        <v>Bottle</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>PRD-086</v>
+      </c>
+      <c r="B87" t="str">
+        <v>SKU-1086</v>
+      </c>
+      <c r="C87" t="str">
+        <v>Silver Sulfadiazine 1% Cream 50g</v>
+      </c>
+      <c r="D87" t="str">
+        <v>Dermatology</v>
+      </c>
+      <c r="E87" t="str">
+        <v>Tube</v>
+      </c>
+      <c r="F87">
+        <v>3600</v>
+      </c>
+      <c r="G87">
+        <v>5400</v>
+      </c>
+      <c r="H87" t="str">
+        <v>Grand Pharma</v>
+      </c>
+      <c r="I87" t="str">
+        <v>Hospital Care</v>
+      </c>
+      <c r="J87" t="str">
+        <v>No</v>
+      </c>
+      <c r="K87" t="str">
+        <v>Silver Sulfadiazine 1% Cream 50g (Silver Sulfadiazine) pharmaceutical grade</v>
+      </c>
+      <c r="L87" t="str">
+        <v>Silver Sulfadiazine</v>
+      </c>
+      <c r="M87" t="str">
+        <v>Silvadene</v>
+      </c>
+      <c r="N87" t="str">
+        <v>Tube</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>PRD-087</v>
+      </c>
+      <c r="B88" t="str">
+        <v>SKU-1087</v>
+      </c>
+      <c r="C88" t="str">
+        <v>Gabapentin 300mg</v>
+      </c>
+      <c r="D88" t="str">
+        <v>CNS &amp; Neurology</v>
+      </c>
+      <c r="E88" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F88">
+        <v>8500</v>
+      </c>
+      <c r="G88">
+        <v>12000</v>
+      </c>
+      <c r="H88" t="str">
+        <v>Grand Pharma</v>
+      </c>
+      <c r="I88" t="str">
+        <v>Specialty Pharma</v>
+      </c>
+      <c r="J88" t="str">
+        <v>No</v>
+      </c>
+      <c r="K88" t="str">
+        <v>Gabapentin 300mg (Gabapentin) pharmaceutical grade</v>
+      </c>
+      <c r="L88" t="str">
+        <v>Gabapentin</v>
+      </c>
+      <c r="M88" t="str">
+        <v>Neurontin</v>
+      </c>
+      <c r="N88" t="str">
+        <v>Capsule</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>PRD-088</v>
+      </c>
+      <c r="B89" t="str">
+        <v>SKU-1088</v>
+      </c>
+      <c r="C89" t="str">
+        <v>Pregabalin 75mg</v>
+      </c>
+      <c r="D89" t="str">
+        <v>CNS &amp; Neurology</v>
+      </c>
+      <c r="E89" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F89">
+        <v>11000</v>
+      </c>
+      <c r="G89">
+        <v>15500</v>
+      </c>
+      <c r="H89" t="str">
+        <v>Grand Pharma</v>
+      </c>
+      <c r="I89" t="str">
+        <v>Specialty Pharma</v>
+      </c>
+      <c r="J89" t="str">
+        <v>No</v>
+      </c>
+      <c r="K89" t="str">
+        <v>Pregabalin 75mg (Pregabalin) pharmaceutical grade</v>
+      </c>
+      <c r="L89" t="str">
+        <v>Pregabalin</v>
+      </c>
+      <c r="M89" t="str">
+        <v>Lyrica</v>
+      </c>
+      <c r="N89" t="str">
+        <v>Capsule</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>PRD-089</v>
+      </c>
+      <c r="B90" t="str">
+        <v>SKU-1089</v>
+      </c>
+      <c r="C90" t="str">
+        <v>Sertraline 50mg</v>
+      </c>
+      <c r="D90" t="str">
+        <v>CNS &amp; Neurology</v>
+      </c>
+      <c r="E90" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F90">
+        <v>9200</v>
+      </c>
+      <c r="G90">
+        <v>13200</v>
+      </c>
+      <c r="H90" t="str">
+        <v>Sun Pharma Group</v>
+      </c>
+      <c r="I90" t="str">
+        <v>Specialty Pharma</v>
+      </c>
+      <c r="J90" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="K90" t="str">
+        <v>Sertraline 50mg (Sertraline) pharmaceutical grade</v>
+      </c>
+      <c r="L90" t="str">
+        <v>Sertraline</v>
+      </c>
+      <c r="M90" t="str">
+        <v>Zoloft</v>
+      </c>
+      <c r="N90" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>PRD-090</v>
+      </c>
+      <c r="B91" t="str">
+        <v>SKU-1090</v>
+      </c>
+      <c r="C91" t="str">
+        <v>Escitalopram 10mg</v>
+      </c>
+      <c r="D91" t="str">
+        <v>CNS &amp; Neurology</v>
+      </c>
+      <c r="E91" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F91">
+        <v>9800</v>
+      </c>
+      <c r="G91">
+        <v>14000</v>
+      </c>
+      <c r="H91" t="str">
+        <v>Sun Pharma Group</v>
+      </c>
+      <c r="I91" t="str">
+        <v>Specialty Pharma</v>
+      </c>
+      <c r="J91" t="str">
+        <v>No</v>
+      </c>
+      <c r="K91" t="str">
+        <v>Escitalopram 10mg (Escitalopram) pharmaceutical grade</v>
+      </c>
+      <c r="L91" t="str">
+        <v>Escitalopram</v>
+      </c>
+      <c r="M91" t="str">
+        <v>Cipralex</v>
+      </c>
+      <c r="N91" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>PRD-091</v>
+      </c>
+      <c r="B92" t="str">
+        <v>SKU-1091</v>
+      </c>
+      <c r="C92" t="str">
+        <v>Betahistine 24mg</v>
+      </c>
+      <c r="D92" t="str">
+        <v>CNS &amp; Neurology</v>
+      </c>
+      <c r="E92" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F92">
+        <v>6800</v>
+      </c>
+      <c r="G92">
+        <v>9800</v>
+      </c>
+      <c r="H92" t="str">
+        <v>Apex Healthcare</v>
+      </c>
+      <c r="I92" t="str">
+        <v>Medical</v>
+      </c>
+      <c r="J92" t="str">
+        <v>No</v>
+      </c>
+      <c r="K92" t="str">
+        <v>Betahistine 24mg (Betahistine Mesilate) pharmaceutical grade</v>
+      </c>
+      <c r="L92" t="str">
+        <v>Betahistine Mesilate</v>
+      </c>
+      <c r="M92" t="str">
+        <v>Serc</v>
+      </c>
+      <c r="N92" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>PRD-092</v>
+      </c>
+      <c r="B93" t="str">
+        <v>SKU-1092</v>
+      </c>
+      <c r="C93" t="str">
+        <v>Flunarizine 5mg</v>
+      </c>
+      <c r="D93" t="str">
+        <v>CNS &amp; Neurology</v>
+      </c>
+      <c r="E93" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F93">
+        <v>4500</v>
+      </c>
+      <c r="G93">
+        <v>6800</v>
+      </c>
+      <c r="H93" t="str">
+        <v>Apex Healthcare</v>
+      </c>
+      <c r="I93" t="str">
+        <v>Medical</v>
+      </c>
+      <c r="J93" t="str">
+        <v>No</v>
+      </c>
+      <c r="K93" t="str">
+        <v>Flunarizine 5mg (Flunarizine) pharmaceutical grade</v>
+      </c>
+      <c r="L93" t="str">
+        <v>Flunarizine</v>
+      </c>
+      <c r="M93" t="str">
+        <v>Sibelium</v>
+      </c>
+      <c r="N93" t="str">
+        <v>Capsule</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>PRD-093</v>
+      </c>
+      <c r="B94" t="str">
+        <v>SKU-1093</v>
+      </c>
+      <c r="C94" t="str">
+        <v>Piracetam 800mg</v>
+      </c>
+      <c r="D94" t="str">
+        <v>CNS &amp; Neurology</v>
+      </c>
+      <c r="E94" t="str">
+        <v>Box</v>
+      </c>
+      <c r="F94">
+        <v>7200</v>
+      </c>
+      <c r="G94">
+        <v>10500</v>
+      </c>
+      <c r="H94" t="str">
+        <v>Grand Pharma</v>
+      </c>
+      <c r="I94" t="str">
+        <v>Medical</v>
+      </c>
+      <c r="J94" t="str">
+        <v>No</v>
+      </c>
+      <c r="K94" t="str">
+        <v>Piracetam 800mg (Piracetam) pharmaceutical grade</v>
+      </c>
+      <c r="L94" t="str">
+        <v>Piracetam</v>
+      </c>
+      <c r="M94" t="str">
+        <v>Nootropil</v>
+      </c>
+      <c r="N94" t="str">
+        <v>Tablet</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>PRD-094</v>
+      </c>
+      <c r="B95" t="str">
+        <v>SKU-1094</v>
+      </c>
+      <c r="C95" t="str">
+        <v>Ciprofloxacin Eye/Ear Drops 5ml</v>
+      </c>
+      <c r="D95" t="str">
+        <v>Ophthalmic &amp; ENT</v>
+      </c>
+      <c r="E95" t="str">
+        <v>Bottle</v>
+      </c>
+      <c r="F95">
+        <v>2800</v>
+      </c>
+      <c r="G95">
+        <v>4200</v>
+      </c>
+      <c r="H95" t="str">
+        <v>Grand Pharma</v>
+      </c>
+      <c r="I95" t="str">
+        <v>Medical</v>
+      </c>
+      <c r="J95" t="str">
+        <v>No</v>
+      </c>
+      <c r="K95" t="str">
+        <v>Ciprofloxacin Eye/Ear Drops 5ml (Ciprofloxacin) pharmaceutical grade</v>
+      </c>
+      <c r="L95" t="str">
+        <v>Ciprofloxacin</v>
+      </c>
+      <c r="M95" t="str">
+        <v>Ciprobay Otic</v>
+      </c>
+      <c r="N95" t="str">
+        <v>Drops</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>PRD-095</v>
+      </c>
+      <c r="B96" t="str">
+        <v>SKU-1095</v>
+      </c>
+      <c r="C96" t="str">
+        <v>Tobramycin + Dexamethasone Eye Drops</v>
+      </c>
+      <c r="D96" t="str">
+        <v>Ophthalmic &amp; ENT</v>
+      </c>
+      <c r="E96" t="str">
+        <v>Bottle</v>
+      </c>
+      <c r="F96">
+        <v>5800</v>
+      </c>
+      <c r="G96">
+        <v>8500</v>
+      </c>
+      <c r="H96" t="str">
+        <v>Novartis Alliance</v>
+      </c>
+      <c r="I96" t="str">
+        <v>Specialty Pharma</v>
+      </c>
+      <c r="J96" t="str">
+        <v>No</v>
+      </c>
+      <c r="K96" t="str">
+        <v>Tobramycin + Dexamethasone Eye Drops (Tobramycin + Dexamethasone) pharmaceutical grade</v>
+      </c>
+      <c r="L96" t="str">
+        <v>Tobramycin + Dexamethasone</v>
+      </c>
+      <c r="M96" t="str">
+        <v>Tobradex</v>
+      </c>
+      <c r="N96" t="str">
+        <v>Drops</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>PRD-096</v>
+      </c>
+      <c r="B97" t="str">
+        <v>SKU-1096</v>
+      </c>
+      <c r="C97" t="str">
+        <v>Sodium Hyaluronate Eye Drops 10ml</v>
+      </c>
+      <c r="D97" t="str">
+        <v>Ophthalmic &amp; ENT</v>
+      </c>
+      <c r="E97" t="str">
+        <v>Bottle</v>
+      </c>
+      <c r="F97">
+        <v>6500</v>
+      </c>
+      <c r="G97">
+        <v>9500</v>
+      </c>
+      <c r="H97" t="str">
+        <v>Novartis Alliance</v>
+      </c>
+      <c r="I97" t="str">
+        <v>Consumer Health</v>
+      </c>
+      <c r="J97" t="str">
+        <v>No</v>
+      </c>
+      <c r="K97" t="str">
+        <v>Sodium Hyaluronate Eye Drops 10ml (Sodium Hyaluronate 0.1%) pharmaceutical grade</v>
+      </c>
+      <c r="L97" t="str">
+        <v>Sodium Hyaluronate 0.1%</v>
+      </c>
+      <c r="M97" t="str">
+        <v>Hialid</v>
+      </c>
+      <c r="N97" t="str">
+        <v>Drops</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>PRD-097</v>
+      </c>
+      <c r="B98" t="str">
+        <v>SKU-1097</v>
+      </c>
+      <c r="C98" t="str">
+        <v>Moxifloxacin Eye Drops 5ml</v>
+      </c>
+      <c r="D98" t="str">
+        <v>Ophthalmic &amp; ENT</v>
+      </c>
+      <c r="E98" t="str">
+        <v>Bottle</v>
+      </c>
+      <c r="F98">
+        <v>7800</v>
+      </c>
+      <c r="G98">
+        <v>11000</v>
+      </c>
+      <c r="H98" t="str">
+        <v>Novartis Alliance</v>
+      </c>
+      <c r="I98" t="str">
+        <v>Specialty Pharma</v>
+      </c>
+      <c r="J98" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="K98" t="str">
+        <v>Moxifloxacin Eye Drops 5ml (Moxifloxacin) pharmaceutical grade</v>
+      </c>
+      <c r="L98" t="str">
+        <v>Moxifloxacin</v>
+      </c>
+      <c r="M98" t="str">
+        <v>Vigamox</v>
+      </c>
+      <c r="N98" t="str">
+        <v>Drops</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>PRD-098</v>
+      </c>
+      <c r="B99" t="str">
+        <v>SKU-1098</v>
+      </c>
+      <c r="C99" t="str">
+        <v>Oxymetazoline 0.05% Nasal Spray 15ml</v>
+      </c>
+      <c r="D99" t="str">
+        <v>Ophthalmic &amp; ENT</v>
+      </c>
+      <c r="E99" t="str">
+        <v>Bottle</v>
+      </c>
+      <c r="F99">
+        <v>3200</v>
+      </c>
+      <c r="G99">
+        <v>4800</v>
+      </c>
+      <c r="H99" t="str">
+        <v>Mega Life Sciences</v>
+      </c>
+      <c r="I99" t="str">
+        <v>Consumer Health</v>
+      </c>
+      <c r="J99" t="str">
+        <v>No</v>
+      </c>
+      <c r="K99" t="str">
+        <v>Oxymetazoline 0.05% Nasal Spray 15ml (Oxymetazoline) pharmaceutical grade</v>
+      </c>
+      <c r="L99" t="str">
+        <v>Oxymetazoline</v>
+      </c>
+      <c r="M99" t="str">
+        <v>Afrin</v>
+      </c>
+      <c r="N99" t="str">
+        <v>Bottle</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>PRD-099</v>
+      </c>
+      <c r="B100" t="str">
+        <v>SKU-1099</v>
+      </c>
+      <c r="C100" t="str">
+        <v>Chloramphenicol 0.5% Eye Drops 10ml</v>
+      </c>
+      <c r="D100" t="str">
+        <v>Ophthalmic &amp; ENT</v>
+      </c>
+      <c r="E100" t="str">
+        <v>Bottle</v>
+      </c>
+      <c r="F100">
+        <v>1800</v>
+      </c>
+      <c r="G100">
+        <v>2700</v>
+      </c>
+      <c r="H100" t="str">
+        <v>Alpha Pharma</v>
+      </c>
+      <c r="I100" t="str">
+        <v>Medical</v>
+      </c>
+      <c r="J100" t="str">
+        <v>No</v>
+      </c>
+      <c r="K100" t="str">
+        <v>Chloramphenicol 0.5% Eye Drops 10ml (Chloramphenicol) pharmaceutical grade</v>
+      </c>
+      <c r="L100" t="str">
+        <v>Chloramphenicol</v>
+      </c>
+      <c r="M100" t="str">
+        <v>Chloromycetin</v>
+      </c>
+      <c r="N100" t="str">
+        <v>Drops</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>PRD-100</v>
+      </c>
+      <c r="B101" t="str">
+        <v>SKU-1100</v>
+      </c>
+      <c r="C101" t="str">
+        <v>Boric Acid Ear Drops 15ml</v>
+      </c>
+      <c r="D101" t="str">
+        <v>Ophthalmic &amp; ENT</v>
+      </c>
+      <c r="E101" t="str">
+        <v>Bottle</v>
+      </c>
+      <c r="F101">
+        <v>1500</v>
+      </c>
+      <c r="G101">
+        <v>2300</v>
+      </c>
+      <c r="H101" t="str">
+        <v>Alpha Pharma</v>
+      </c>
+      <c r="I101" t="str">
+        <v>Consumer Health</v>
+      </c>
+      <c r="J101" t="str">
+        <v>No</v>
+      </c>
+      <c r="K101" t="str">
+        <v>Boric Acid Ear Drops 15ml (Boric Acid Solution) pharmaceutical grade</v>
+      </c>
+      <c r="L101" t="str">
+        <v>Boric Acid Solution</v>
+      </c>
+      <c r="M101" t="str">
+        <v>Oto-Clean</v>
+      </c>
+      <c r="N101" t="str">
+        <v>Drops</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N101"/>
   </ignoredErrors>
 </worksheet>
 </file>